--- a/job_application_forms/017_telecom_network_specialist_employment_form--job_application_forms.xlsx
+++ b/job_application_forms/017_telecom_network_specialist_employment_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>job_type_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Job Type</t>
+          <t>Job Type 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>job_category</t>
+          <t>job_category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Job Category</t>
+          <t>Job Category 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1103,7 +1103,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>job_title_choices</t>
+          <t>job_title_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1409,7 +1409,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>job_category_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1426,7 +1426,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_category_choices</t>
+          <t>job_category_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
